--- a/Groupes MIA.xlsx
+++ b/Groupes MIA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulf\OneDrive\Documents\7. Doctorat\1. Cours\11. Cours MIA Siren\MIA_IREN-MTM_2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18A4906-1ABD-4F89-B256-844E533BBA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374737EB-09C0-4E64-83A7-6B725DB22D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4284" yWindow="1296" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Groupe</t>
   </si>
@@ -79,13 +79,25 @@
   </si>
   <si>
     <t>Prénom Nom</t>
+  </si>
+  <si>
+    <t>MrHashFox0x</t>
+  </si>
+  <si>
+    <t>https://github.com/clararosier</t>
+  </si>
+  <si>
+    <t>https://github.com/05cl</t>
+  </si>
+  <si>
+    <t>https://github.com/Amaryyyy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -102,6 +114,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -123,15 +142,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -348,13 +370,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="51.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -362,15 +384,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -378,7 +403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -386,7 +411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -394,7 +419,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -402,7 +427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -410,7 +435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -418,7 +443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -426,7 +451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -434,15 +459,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
@@ -450,7 +478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -458,7 +486,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>4</v>
       </c>
@@ -466,15 +494,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>5</v>
       </c>
@@ -482,15 +513,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>5</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C11" r:id="rId1" display="https://github.com/MrHashFox0x" xr:uid="{652BB33A-4557-4F9E-ADB0-74B09F23CFE8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Groupes MIA.xlsx
+++ b/Groupes MIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulf\OneDrive\Documents\7. Doctorat\1. Cours\11. Cours MIA Siren\MIA_IREN-MTM_2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374737EB-09C0-4E64-83A7-6B725DB22D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FCD7CA-3CD4-4F34-894A-C6A00DB81BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4284" yWindow="1296" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Groupe</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Gabin Sorge</t>
   </si>
   <si>
-    <t xml:space="preserve"> Stanislas Prevost</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amary Le Bideau,, </t>
   </si>
   <si>
@@ -84,13 +81,40 @@
     <t>MrHashFox0x</t>
   </si>
   <si>
-    <t>https://github.com/clararosier</t>
-  </si>
-  <si>
-    <t>https://github.com/05cl</t>
-  </si>
-  <si>
-    <t>https://github.com/Amaryyyy</t>
+    <t>Maïka</t>
+  </si>
+  <si>
+    <t>louisegiroud</t>
+  </si>
+  <si>
+    <t>Gillennn</t>
+  </si>
+  <si>
+    <t>gabinsrg</t>
+  </si>
+  <si>
+    <t>Faatimafk</t>
+  </si>
+  <si>
+    <t>clararosier</t>
+  </si>
+  <si>
+    <t>celiagarjahb</t>
+  </si>
+  <si>
+    <t>Stanislas Prevost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amaryyyy Collaborator </t>
+  </si>
+  <si>
+    <t>NicoJuni</t>
+  </si>
+  <si>
+    <t>noaasmith</t>
+  </si>
+  <si>
+    <t>STan stanis</t>
   </si>
 </sst>
 </file>
@@ -381,7 +405,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -391,8 +415,8 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -410,6 +434,9 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -418,6 +445,9 @@
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -426,6 +456,9 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -434,6 +467,9 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -450,6 +486,9 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -458,6 +497,9 @@
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -467,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -477,6 +519,9 @@
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -485,6 +530,9 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -493,16 +541,19 @@
       <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="15" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -510,7 +561,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -518,15 +572,28 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="https://github.com/MrHashFox0x" xr:uid="{652BB33A-4557-4F9E-ADB0-74B09F23CFE8}"/>
+    <hyperlink ref="C5" r:id="rId2" display="https://github.com/maika-f" xr:uid="{5A56E0FF-EEA6-4A3C-9487-B257B35211AF}"/>
+    <hyperlink ref="C10" r:id="rId3" display="https://github.com/louisegiroud" xr:uid="{7E385141-CE3F-4F72-B316-91FD6E001398}"/>
+    <hyperlink ref="C4" r:id="rId4" display="https://github.com/Gillennn" xr:uid="{E6EEF36E-9DBB-44FE-AEA4-1258324EBC0E}"/>
+    <hyperlink ref="C14" r:id="rId5" display="https://github.com/gabinsrg" xr:uid="{A535173B-9C52-4044-A991-AD6E99010271}"/>
+    <hyperlink ref="C13" r:id="rId6" display="https://github.com/Faatimafk" xr:uid="{B67BA419-EB85-4F63-A0C7-008801D7CD93}"/>
+    <hyperlink ref="C2" r:id="rId7" display="https://github.com/clararosier" xr:uid="{0F3631AE-A722-4851-953E-83C896F927E6}"/>
+    <hyperlink ref="C12" r:id="rId8" display="https://github.com/celiagarjahb" xr:uid="{3E5597E8-6B73-475E-A89D-20D2C527F773}"/>
+    <hyperlink ref="C15" r:id="rId9" display="https://github.com/Amaryyyy" xr:uid="{A0927CD5-57F2-4F6F-A97C-C6ADF94BFC75}"/>
+    <hyperlink ref="C17" r:id="rId10" display="https://github.com/05cl" xr:uid="{765F8692-E2D1-4C76-B4C6-39386D6D123F}"/>
+    <hyperlink ref="C9" r:id="rId11" display="https://github.com/NicoJuni" xr:uid="{37E3F379-8EFC-4127-871A-6FD6851EBD38}"/>
+    <hyperlink ref="C7" r:id="rId12" display="https://github.com/noaasmith" xr:uid="{4EF58982-9D29-47E1-B600-A45A23626009}"/>
+    <hyperlink ref="C6" r:id="rId13" display="https://github.com/raphaeltzl" xr:uid="{FF1DA069-752E-4D98-B101-F3D6B7DF6EA5}"/>
+    <hyperlink ref="C16" r:id="rId14" display="https://github.com/stanislasprevost" xr:uid="{10A1BC2A-D3A3-4A8E-8EBA-535950A1F4FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
